--- a/public/templates/preguntas-plantilla.xlsx
+++ b/public/templates/preguntas-plantilla.xlsx
@@ -1,45 +1,150 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gerar\OneDrive\Escritorio\Proyectos\Harry Potter estudio\fluffys-2\public\templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2663A2-9BF3-403D-9433-0247CDD3630A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="1440" yWindow="1728" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Preguntas" sheetId="1" r:id="rId1"/>
     <sheet name="Instrucciones" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="categorias">Instrucciones!$A$17:$A$32</definedName>
+  </definedNames>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>bookId</t>
+  </si>
+  <si>
+    <t>chapter</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>prompt</t>
+  </si>
+  <si>
+    <t>correctAnswer</t>
+  </si>
+  <si>
+    <t>Personaje</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Hechizo o encantamiento</t>
+  </si>
+  <si>
+    <t>Reglas del Excel para Fluffys 2</t>
+  </si>
+  <si>
+    <t>Columnas obligatorias</t>
+  </si>
+  <si>
+    <t>bookId, chapter, category, prompt, correctAnswer</t>
+  </si>
+  <si>
+    <t>Columnas opcionales</t>
+  </si>
+  <si>
+    <t>hp5, hp6 o hp7. También se acepta 5, 6 o 7.</t>
+  </si>
+  <si>
+    <t>Entero. HP5: 1–38. HP6: 1–30. HP7: 1–36.</t>
+  </si>
+  <si>
+    <t>Debe coincidir exactamente con una categoría permitida:</t>
+  </si>
+  <si>
+    <t>Organización</t>
+  </si>
+  <si>
+    <t>Ley - decreto</t>
+  </si>
+  <si>
+    <t>Poción</t>
+  </si>
+  <si>
+    <t>Criatura</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Lugar</t>
+  </si>
+  <si>
+    <t>Profecía</t>
+  </si>
+  <si>
+    <t>Muerte</t>
+  </si>
+  <si>
+    <t>Medio</t>
+  </si>
+  <si>
+    <t>Educación</t>
+  </si>
+  <si>
+    <t>Nota / curiosidad</t>
+  </si>
+  <si>
+    <t>Recuerdo</t>
+  </si>
+  <si>
+    <t>Artefacto u objeto</t>
+  </si>
+  <si>
+    <t>Horrocrux</t>
+  </si>
+  <si>
+    <t>Obligatorio. Máximo 500 caracteres.</t>
+  </si>
+  <si>
+    <t>Obligatorio. Máximo 300 caracteres.</t>
+  </si>
+  <si>
+    <t>Notas</t>
+  </si>
+  <si>
+    <t>Una pregunta por fila. La primera hoja debe llamarse Preguntas o ser la primera del archivo.</t>
+  </si>
+  <si>
+    <t>La sección no se incluye: Fluffys 2 la calcula a partir del capítulo.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -66,13 +171,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,289 +510,244 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="25.83203125" customWidth="1"/>
-    <col min="5" max="5" width="70.83203125" customWidth="1"/>
-    <col min="6" max="6" width="45.83203125" customWidth="1"/>
-    <col min="7" max="7" width="40.83203125" customWidth="1"/>
+    <col min="1" max="1" width="24.69921875" customWidth="1"/>
+    <col min="2" max="3" width="10.69921875" customWidth="1"/>
+    <col min="4" max="4" width="25.69921875" customWidth="1"/>
+    <col min="5" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="45.69921875" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>bookId</v>
-      </c>
-      <c r="C1" t="str">
-        <v>chapter</v>
-      </c>
-      <c r="D1" t="str">
-        <v>category</v>
-      </c>
-      <c r="E1" t="str">
-        <v>prompt</v>
-      </c>
-      <c r="F1" t="str">
-        <v>correctAnswer</v>
-      </c>
-      <c r="G1" t="str">
-        <v>incorrectAnswers</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>hp5-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>hp5</v>
-      </c>
-      <c r="C2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" t="str">
-        <v>Personaje</v>
-      </c>
-      <c r="E2" t="str">
-        <v>¿Quién es el nuevo profesor de Defensa Contra las Artes Oscuras?</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Dolores Umbridge</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Severus Snape|Remus Lupin|Alastor Moody</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v/>
-      </c>
-      <c r="B3" t="str">
-        <v>hp5</v>
-      </c>
-      <c r="C3">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" t="str">
-        <v>Hechizo o encantamiento</v>
-      </c>
-      <c r="E3" t="str">
-        <v>¿Qué hechizo usa Harry contra los dementores?</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Expecto Patronum</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Expelliarmus|Stupefy|Protego</v>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{FFC3CB3A-3C7B-414A-82A3-5D5F5889E2D6}">
+      <formula1>categorias</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B13 B72:B1048576" xr:uid="{FDD62239-4CCD-4B10-A40E-A7335C08FAE8}">
+      <formula1>"hp1,hp2,hp3,hp4,hp5,hp6,hp7"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError sqref="A1:F1 A3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A46"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:A42"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="80.83203125" customWidth="1"/>
+    <col min="1" max="1" width="80.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Reglas del Excel para Fluffys 2</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Columnas obligatorias</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>bookId, chapter, category, prompt, correctAnswer</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Columnas opcionales</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>id, incorrectAnswers</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>bookId</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>hp5, hp6 o hp7. También se acepta 5, 6 o 7.</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>chapter</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Entero. HP5: 1–38. HP6: 1–30. HP7: 1–36.</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>category</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Debe coincidir exactamente con una categoría permitida:</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Personaje</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Hechizo o encantamiento</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Organización</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Ley - decreto</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Poción</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Criatura</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>Fecha</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>Lugar</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Profecía</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Muerte</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Medio</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Educación</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>Nota / curiosidad</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>Recuerdo</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>Artefacto u objeto</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Horrocrux</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>prompt</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Obligatorio. Máximo 500 caracteres.</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>correctAnswer</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>Obligatorio. Máximo 300 caracteres.</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>incorrectAnswers</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>Opcional. Respuestas incorrectas separadas por |</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>Ejemplo: Severus Snape|Remus Lupin|Alastor Moody</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>Notas</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>Una pregunta por fila. La primera hoja debe llamarse Preguntas o ser la primera del archivo.</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>La sección no se incluye: Fluffys 2 la calcula a partir del capítulo.</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A46"/>
+    <ignoredError sqref="A1:A6 A43 A8:A39" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/preguntas-plantilla.xlsx
+++ b/public/templates/preguntas-plantilla.xlsx
@@ -68,7 +68,7 @@
     <t>hp5, hp6 o hp7. También se acepta 5, 6 o 7.</t>
   </si>
   <si>
-    <t>Entero. HP5: 1–38. HP6: 1–30. HP7: 1–36.</t>
+    <t>Entero. HP5: 1–38. HP6: 1–30. HP7: 1–37.</t>
   </si>
   <si>
     <t>Debe coincidir exactamente con una categoría permitida:</t>
